--- a/Documents/E-commerce Store Test_Cases.xlsx
+++ b/Documents/E-commerce Store Test_Cases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Software Testing\Interview Prep\Projects\Automation Test Store (Automation)\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62C582D-2C94-4FF5-8366-B81987D929BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A864410D-A172-43FC-9306-5EBACB3B3917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{458D6809-A548-454C-9F49-BADA77EB5556}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="198">
   <si>
     <t>TC_ID</t>
   </si>
@@ -171,9 +171,6 @@
     <t>TS_004</t>
   </si>
   <si>
-    <t>Verify login with valid credentials</t>
-  </si>
-  <si>
     <t>Positive</t>
   </si>
   <si>
@@ -187,14 +184,6 @@
   </si>
   <si>
     <t>Medium</t>
-  </si>
-  <si>
-    <t>Login Name: testuser01
-Password: testuser@123</t>
-  </si>
-  <si>
-    <t>Login Name: test01
-Password: test@123</t>
   </si>
   <si>
     <t>TS_008</t>
@@ -532,9 +521,6 @@
 </t>
   </si>
   <si>
-    <t>Relevant products displayed</t>
-  </si>
-  <si>
     <t xml:space="preserve">1. Enter invalid keyword
 2. Perform search
 </t>
@@ -557,9 +543,6 @@
     <t xml:space="preserve">1. Enter invalid coupon code
 2. Apply coupon
 </t>
-  </si>
-  <si>
-    <t>Error message displayed and no discount applied</t>
   </si>
   <si>
     <t>Product available in cart</t>
@@ -571,15 +554,7 @@
 </t>
   </si>
   <si>
-    <t>User navigates to payment page</t>
-  </si>
-  <si>
     <t>On payment page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enter valid payment details
-2. Confirm order
-</t>
   </si>
   <si>
     <t>Order confirmation displayed with order ID</t>
@@ -596,13 +571,6 @@
   <si>
     <t>User logged in
 Product available in stock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.Open any product detail page
-2.Note the unit price
-3.Increase the quantity
-4.Add product to cart
-</t>
   </si>
   <si>
     <t>Cart total reflects correct calculation (unit price × quantity)</t>
@@ -692,17 +660,55 @@
     <t>-</t>
   </si>
   <si>
-    <t xml:space="preserve">First Name: username_01
-Last Name: lastname_01
-E-Mail: testuser_01@gmail.com
+    <t xml:space="preserve">First Name: username_001
+Last Name: lastname_001
+E-Mail: testuser_001@gmail.com
 Address: Gandhi nagar
 City: Vijayawada
 Country:  India
 State: Andhra Pradesh
 ZIP Code: 500046
-Login name: testuser_01
-Password: testuser@123
-Confirm Password: testuser@123
+Login name: testuser_001
+Password: testuser@001
+Confirm Password: testuser@001
+</t>
+  </si>
+  <si>
+    <t>Verify login with In-valid credentials</t>
+  </si>
+  <si>
+    <t>Verify login with Valid credentials</t>
+  </si>
+  <si>
+    <t>Login Name: testuser_001
+Password: testuser@001</t>
+  </si>
+  <si>
+    <t>Login Name: testuser_001
+Password: test@123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Open any product detail page
+2.Note the unit price
+3.Increase the quantity
+4.Verify the product price
+</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Page redirected to irrelavant product page</t>
+  </si>
+  <si>
+    <t>User navigates to Checkout Confirmationpage</t>
+  </si>
+  <si>
+    <t>Error message displayed as  discount code expired ot not applicable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter or Verify valid payment details
+2. Confirm order
 </t>
   </si>
 </sst>
@@ -747,7 +753,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -769,6 +775,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF3300"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -811,10 +823,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -825,6 +837,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF3300"/>
       <color rgb="FF996633"/>
     </mruColors>
   </colors>
@@ -1210,34 +1223,34 @@
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>193</v>
+        <v>44</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="93.6" x14ac:dyDescent="0.3">
@@ -1254,16 +1267,16 @@
         <v>16</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>11</v>
@@ -1271,7 +1284,9 @@
       <c r="J3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="2"/>
+      <c r="K3" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="4" spans="1:11" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -1284,52 +1299,54 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K4" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>44</v>
+        <v>188</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>51</v>
+        <v>191</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>11</v>
@@ -1337,659 +1354,699 @@
       <c r="J5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="2"/>
+      <c r="K5" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="6" spans="1:11" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="2"/>
+      <c r="K6" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="7" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K7" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="8" spans="1:11" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K8" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="9" spans="1:11" ht="78" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K9" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="10" spans="1:11" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K10" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="11" spans="1:11" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K11" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="12" spans="1:11" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="E12" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K12" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="13" spans="1:11" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K13" s="2"/>
+        <v>65</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="14" spans="1:11" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K14" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="15" spans="1:11" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="H15" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="2"/>
+      <c r="K15" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="78" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="H16" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K16" s="2"/>
+        <v>65</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="17" spans="1:11" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="H17" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K17" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="18" spans="1:11" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K18" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="19" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K19" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="20" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K20" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="21" spans="1:11" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K21" s="2"/>
+        <v>65</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="22" spans="1:11" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K22" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="23" spans="1:11" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K23" s="2"/>
+      <c r="K23" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="24" spans="1:11" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K24" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="25" spans="1:11" ht="78" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>11</v>
@@ -1997,106 +2054,114 @@
       <c r="J25" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K25" s="2"/>
-    </row>
-    <row r="26" spans="1:11" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="K25" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="78" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K26" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="27" spans="1:11" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K27" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="28" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K28" s="4"/>
+        <v>44</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="34" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E34" t="s">
